--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627915</v>
+        <v>129622139</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1121,20 +1121,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601358</v>
+        <v>601331</v>
       </c>
       <c r="R6" t="n">
         <v>6977323</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,11 +1168,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>65 ca stycken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129622139</v>
+        <v>129627915</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1223,24 +1222,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601331</v>
+        <v>601358</v>
       </c>
       <c r="R7" t="n">
         <v>6977323</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>65 ca stycken</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129622139</v>
+        <v>129627915</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1121,24 +1121,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601331</v>
+        <v>601358</v>
       </c>
       <c r="R6" t="n">
         <v>6977323</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>65 ca stycken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627915</v>
+        <v>129622139</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1222,20 +1223,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601358</v>
+        <v>601331</v>
       </c>
       <c r="R7" t="n">
         <v>6977323</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>65 ca stycken</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129622034</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129627917</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129622220</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129627915</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>129622139</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>129622098</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>129627914</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>129627918</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129627919</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>129627920</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129622034</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129627917</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129622220</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129627915</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>129622139</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>129622098</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>129627914</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>129627918</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129627919</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>129627920</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129622034</v>
+        <v>129627917</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601333</v>
+        <v>601363</v>
       </c>
       <c r="R3" t="n">
-        <v>6977420</v>
+        <v>6977334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>5 stycken ca kan finnas mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129627917</v>
+        <v>129627915</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601363</v>
+        <v>601358</v>
       </c>
       <c r="R4" t="n">
-        <v>6977334</v>
+        <v>6977323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5 stycken ca kan finnas mer i blåbärsriset</t>
+          <t>65 ca stycken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,38 +981,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129622220</v>
+        <v>129622139</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,13 +1020,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601297</v>
+        <v>601331</v>
       </c>
       <c r="R5" t="n">
-        <v>6977298</v>
+        <v>6977323</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129627915</v>
+        <v>129622098</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,17 +1110,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601358</v>
+        <v>601355</v>
       </c>
       <c r="R6" t="n">
-        <v>6977323</v>
+        <v>6977381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1157,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>65 ca stycken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129622139</v>
+        <v>129627914</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,24 +1211,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601331</v>
+        <v>601382</v>
       </c>
       <c r="R7" t="n">
-        <v>6977323</v>
+        <v>6977291</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,6 +1254,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>80 ca ( troligtvis mer)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129622098</v>
+        <v>129627918</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,21 +1313,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601355</v>
+        <v>601371</v>
       </c>
       <c r="R8" t="n">
-        <v>6977381</v>
+        <v>6977369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1356,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>27 ca stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627914</v>
+        <v>129627919</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601382</v>
+        <v>601366</v>
       </c>
       <c r="R9" t="n">
-        <v>6977291</v>
+        <v>6977390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1462,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>80 ca ( troligtvis mer)</t>
+          <t>19 stycken ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627918</v>
+        <v>129627920</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601371</v>
+        <v>601359</v>
       </c>
       <c r="R10" t="n">
-        <v>6977369</v>
+        <v>6977390</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,7 +1564,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>27 ca stycken</t>
+          <t>61 stycken ca</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,45 +1591,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129627919</v>
+        <v>129622034</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601366</v>
+        <v>601333</v>
       </c>
       <c r="R11" t="n">
-        <v>6977390</v>
+        <v>6977420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>19 stycken ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,45 +1698,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627920</v>
+        <v>129622220</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rågsvedjeberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601359</v>
+        <v>601297</v>
       </c>
       <c r="R12" t="n">
-        <v>6977390</v>
+        <v>6977298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>61 stycken ca</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129627917</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129627915</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129622139</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>129622098</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129627914</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129627918</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129627919</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129627920</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129627917</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129627915</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129622139</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>129622098</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129627914</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129627918</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129627919</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129627920</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129627917</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129627915</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129622139</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>129622098</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129627914</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129627918</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129627919</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129627920</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129627917</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129627915</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129622139</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>129622098</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129627914</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129627918</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129627919</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129627920</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1594,7 +1594,7 @@
         <v>129622034</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>129622220</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129627916</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129627917</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129627915</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129622139</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>129622098</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>129627914</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129627918</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129627919</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>129627920</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B13" t="n">
-        <v>91808</v>
+        <v>57881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R13" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>91808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R14" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>91808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R13" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B14" t="n">
-        <v>91808</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R14" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>131108166</v>
       </c>
       <c r="B15" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131108169</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B13" t="n">
-        <v>91809</v>
+        <v>57881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R13" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>91809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R14" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>91809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R13" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B14" t="n">
-        <v>91809</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R14" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>91810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R13" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B14" t="n">
-        <v>91809</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R14" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,7 +2040,7 @@
         <v>131108166</v>
       </c>
       <c r="B15" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131108169</v>
       </c>
       <c r="B16" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B13" t="n">
-        <v>91810</v>
+        <v>57881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R13" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>91810</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R14" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>91813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R13" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B14" t="n">
-        <v>91810</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R14" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2165,7 @@
         <v>131108169</v>
       </c>
       <c r="B16" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>57881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R13" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>91814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R14" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,7 +2040,7 @@
         <v>131108166</v>
       </c>
       <c r="B15" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131108169</v>
       </c>
       <c r="B16" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>91814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R13" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B14" t="n">
-        <v>91814</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R14" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B13" t="n">
-        <v>91814</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R13" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>91816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R14" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,7 +2040,7 @@
         <v>131108166</v>
       </c>
       <c r="B15" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131108169</v>
       </c>
       <c r="B16" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26429-2025 artfynd.xlsx
+++ b/artfynd/A 26429-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131108277</v>
+        <v>131108314</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601141</v>
+        <v>601153</v>
       </c>
       <c r="R13" t="n">
-        <v>6977358</v>
+        <v>6977380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-1083</t>
+          <t>2025-1088</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131108314</v>
+        <v>131108277</v>
       </c>
       <c r="B14" t="n">
-        <v>91816</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601153</v>
+        <v>601141</v>
       </c>
       <c r="R14" t="n">
-        <v>6977380</v>
+        <v>6977358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-1088</t>
+          <t>2025-1083</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,7 +2040,7 @@
         <v>131108166</v>
       </c>
       <c r="B15" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131108169</v>
       </c>
       <c r="B16" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
